--- a/4_analisis/salidas/secciones/tablas_secciones.xlsx
+++ b/4_analisis/salidas/secciones/tablas_secciones.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Peso de las secciones en 2026</t>
+          <t>Peso de las secciones en 2027</t>
         </is>
       </c>
     </row>
@@ -470,7 +470,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Importe 2026 (M€)</t>
+          <t>Importe 2027 (M€)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4542.9</v>
+        <v>4928.7</v>
       </c>
       <c r="D5" t="n">
-        <v>38.15</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="6">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2314.9</v>
+        <v>2532.9</v>
       </c>
       <c r="D6" t="n">
-        <v>19.44</v>
+        <v>20.19</v>
       </c>
     </row>
     <row r="7">
@@ -527,10 +527,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>985</v>
+        <v>1056.5</v>
       </c>
       <c r="D7" t="n">
-        <v>8.27</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="8">
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>837.7</v>
+        <v>1035</v>
       </c>
       <c r="D8" t="n">
-        <v>7.03</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>523.3</v>
+        <v>551.1</v>
       </c>
       <c r="D9" t="n">
         <v>4.39</v>
@@ -572,7 +572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TRANSICIÓN ECOLÓGICA Y ENERGÍA (12)</t>
+          <t>UNIVERSIDADES, CIENCIA E INNOVACIÓN Y CULTURA (17)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -581,16 +581,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>456.6</v>
+        <v>438.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.83</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UNIVERSIDADES, CIENCIA E INNOVACIÓN Y CULTURA (17)</t>
+          <t>CONSEJ. PRESIDENCIA, ADMONES. PÚBL.,JUSTICIA Y SEG (08)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,34 +599,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>424.5</v>
+        <v>430.6</v>
       </c>
       <c r="D11" t="n">
-        <v>3.56</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CONSEJ. PRESIDENCIA, ADMONES. PÚBL.,JUSTICIA Y SEG (08)</t>
+          <t>DIVERSAS CONSEJERÍAS (19)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Consejerías</t>
+          <t>Secciones no departamentales</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>386.7</v>
+        <v>260.4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.25</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TURISMO Y EMPLEO (16)</t>
+          <t>PRESIDENCIA DEL GOBIERNO (06)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>262.6</v>
+        <v>226.9</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DIVERSAS CONSEJERÍAS (19)</t>
+          <t>HACIENDA Y RELACIONES CON LA UNIÓN EUROPEA (10)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Secciones no departamentales</t>
+          <t>Consejerías</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>252.1</v>
+        <v>223.2</v>
       </c>
       <c r="D14" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HACIENDA Y RELACIONES CON LA UNIÓN EUROPEA (10)</t>
+          <t>TURISMO Y EMPLEO (16)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>234.7</v>
+        <v>205.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRESIDENCIA DEL GOBIERNO (06)</t>
+          <t>AGRICULTURA,GANADERÍA,PESCA Y SOBERNÍA ALIMENTARIA (13)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -689,34 +689,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>223.2</v>
+        <v>154.7</v>
       </c>
       <c r="D16" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AGRICULTURA,GANADERÍA,PESCA Y SOBERNÍA ALIMENTARIA (13)</t>
+          <t>DEUDA PÚBLICA (05)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Consejerías</t>
+          <t>Secciones no departamentales</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>156.1</v>
+        <v>150.8</v>
       </c>
       <c r="D17" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POLÍTICA TERRITORIAL, COHESIÓN TERRITORIAL Y AGUAS (09)</t>
+          <t>TRANSICIÓN ECOLÓGICA Y ENERGÍA (12)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>111.5</v>
+        <v>145.4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DEUDA PÚBLICA (05)</t>
+          <t>POLÍTICA TERRITORIAL, COHESIÓN TERRITORIAL Y AGUAS (09)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Secciones no departamentales</t>
+          <t>Consejerías</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>104.6</v>
+        <v>107.5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="20">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="22">
@@ -827,7 +827,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Estructura 2026 retroproyectada (M€)</t>
+          <t>Estructura 2027 retroproyectada (M€)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>191,4</t>
+          <t>191,8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>159,9</t>
+          <t>160,3</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>272,7</t>
+          <t>272,5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-133,2</t>
+          <t>-133,5</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>111,9</t>
+          <t>114,8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>111,9</t>
+          <t>114,8</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>143,3</t>
+          <t>141,9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-78,4</t>
+          <t>-79,9</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>537,4</t>
+          <t>537,2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,6</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>188,0</t>
+          <t>185,1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-73,6</t>
+          <t>-76,6</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>168,4</t>
+          <t>168,3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>80,0</t>
+          <t>79,1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-159,7</t>
+          <t>-160,6</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>253,8</t>
+          <t>253,6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80,3</t>
+          <t>80,2</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>400,0</t>
+          <t>399,1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>400,0</t>
+          <t>399,1</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.999,3</t>
+          <t>1.999,7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-328,4</t>
+          <t>-328,0</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>254,2</t>
+          <t>258,1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14,7</t>
+          <t>18,6</t>
         </is>
       </c>
     </row>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>684,8</t>
+          <t>684,1</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>2,5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Nota. Estructura de consejerías de 2026 retroproyectada con la tabla 2.16. Elaboración propia.</t>
+          <t>Nota. Estructura de consejerías de 2027 retroproyectada con la tabla 2.16. Elaboración propia.</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1386,22 +1386,37 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>2026</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>447,4</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>3,8</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>8,6</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Nota. Servicios etiquetados en la tabla 2.2. Elaboración propia.</t>
         </is>
